--- a/examples/sample_output/CDE-2018-0117_application.xlsx
+++ b/examples/sample_output/CDE-2018-0117_application.xlsx
@@ -862,7 +862,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>CY2025  |  Prepared: May 08, 2026  |  Readiness Grade: A (86.6/100)</t>
+          <t>CY2025  |  Prepared: May 09, 2026  |  Readiness Grade: A (86.6/100)</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>CONFIDENTIAL — Heartland Impact CDE, LLC — NMTC CY2025 — Generated 2026-05-08</t>
+          <t>CONFIDENTIAL — Heartland Impact CDE, LLC — NMTC CY2025 — Generated 2026-05-09</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Heartland Impact CDE, LLC  |  CY2025  |  Generated 2026-05-08</t>
+          <t>Heartland Impact CDE, LLC  |  CY2025  |  Generated 2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Heartland Impact CDE, LLC  |  CY2025  |  Generated 2026-05-08</t>
+          <t>Heartland Impact CDE, LLC  |  CY2025  |  Generated 2026-05-09</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Heartland Impact CDE, LLC  |  CY2025  |  Generated 2026-05-08</t>
+          <t>Heartland Impact CDE, LLC  |  CY2025  |  Generated 2026-05-09</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Heartland Impact CDE, LLC  |  CY2025  |  Generated 2026-05-08</t>
+          <t>Heartland Impact CDE, LLC  |  CY2025  |  Generated 2026-05-09</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Heartland Impact CDE, LLC  |  CY2025  |  Generated 2026-05-08</t>
+          <t>Heartland Impact CDE, LLC  |  CY2025  |  Generated 2026-05-09</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Heartland Impact CDE, LLC  |  CY2025  |  Generated 2026-05-08</t>
+          <t>Heartland Impact CDE, LLC  |  CY2025  |  Generated 2026-05-09</t>
         </is>
       </c>
     </row>
